--- a/frontend/public/templates/scores/v1/teaching-g23-teaching-quality.xlsx
+++ b/frontend/public/templates/scores/v1/teaching-g23-teaching-quality.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="R5c4d23941f7146e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="Rb9989fa326544ffc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -347,6 +347,10 @@
     <x:col min="27" max="27" width="16" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="16" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="16" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="16" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="16" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="16" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -368,12 +372,20 @@
         <x:v>标准差</x:v>
       </x:c>
       <x:c r="H1" s="8" t="str">
+        <x:v>语文</x:v>
+      </x:c>
+      <x:c r="I1" s="8" t="str">
+        <x:v>数学</x:v>
+      </x:c>
+      <x:c r="J1" s="8" t="str">
+        <x:v>英语</x:v>
+      </x:c>
+      <x:c r="K1" s="8" t="str">
+        <x:v>三大门</x:v>
+      </x:c>
+      <x:c r="L1" s="8" t="str">
         <x:v>等级人数及比率</x:v>
       </x:c>
-      <x:c r="I1" s="8"/>
-      <x:c r="J1" s="8"/>
-      <x:c r="K1" s="8"/>
-      <x:c r="L1" s="8"/>
       <x:c r="M1" s="8"/>
       <x:c r="N1" s="8"/>
       <x:c r="O1" s="8"/>
@@ -391,6 +403,10 @@
       <x:c r="AA1" s="8"/>
       <x:c r="AB1" s="8"/>
       <x:c r="AC1" s="8"/>
+      <x:c r="AD1" s="8"/>
+      <x:c r="AE1" s="8"/>
+      <x:c r="AF1" s="8"/>
+      <x:c r="AG1" s="8"/>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8"/>
@@ -408,70 +424,74 @@
         <x:v>等级</x:v>
       </x:c>
       <x:c r="G2" s="8"/>
-      <x:c r="H2" s="8" t="str">
+      <x:c r="H2" s="8"/>
+      <x:c r="I2" s="8"/>
+      <x:c r="J2" s="8"/>
+      <x:c r="K2" s="8"/>
+      <x:c r="L2" s="8" t="str">
         <x:v>A+</x:v>
-      </x:c>
-      <x:c r="I2" s="8" t="str">
-        <x:v>比率</x:v>
-      </x:c>
-      <x:c r="J2" s="8" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K2" s="8" t="str">
-        <x:v>比率</x:v>
-      </x:c>
-      <x:c r="L2" s="8" t="str">
-        <x:v>B+</x:v>
       </x:c>
       <x:c r="M2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="N2" s="8" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="O2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="P2" s="8" t="str">
-        <x:v>B-</x:v>
+        <x:v>B+</x:v>
       </x:c>
       <x:c r="Q2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="R2" s="8" t="str">
-        <x:v>C+</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="S2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="T2" s="8" t="str">
-        <x:v>C</x:v>
+        <x:v>B-</x:v>
       </x:c>
       <x:c r="U2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="V2" s="8" t="str">
-        <x:v>C-</x:v>
+        <x:v>C+</x:v>
       </x:c>
       <x:c r="W2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="X2" s="8" t="str">
-        <x:v>D+</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="Y2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="Z2" s="8" t="str">
-        <x:v>D</x:v>
+        <x:v>C-</x:v>
       </x:c>
       <x:c r="AA2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
       <x:c r="AB2" s="8" t="str">
+        <x:v>D+</x:v>
+      </x:c>
+      <x:c r="AC2" s="8" t="str">
+        <x:v>比率</x:v>
+      </x:c>
+      <x:c r="AD2" s="8" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="AE2" s="8" t="str">
+        <x:v>比率</x:v>
+      </x:c>
+      <x:c r="AF2" s="8" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="AC2" s="8" t="str">
+      <x:c r="AG2" s="8" t="str">
         <x:v>比率</x:v>
       </x:c>
     </x:row>
@@ -483,10 +503,10 @@
       <x:c r="E3" s="14"/>
       <x:c r="F3" s="14"/>
       <x:c r="G3" s="14"/>
-      <x:c r="H3" s="13"/>
-      <x:c r="I3" s="15"/>
-      <x:c r="J3" s="13"/>
-      <x:c r="K3" s="15"/>
+      <x:c r="H3" s="14"/>
+      <x:c r="I3" s="14"/>
+      <x:c r="J3" s="14"/>
+      <x:c r="K3" s="14"/>
       <x:c r="L3" s="13"/>
       <x:c r="M3" s="15"/>
       <x:c r="N3" s="13"/>
@@ -505,6 +525,10 @@
       <x:c r="AA3" s="15"/>
       <x:c r="AB3" s="13"/>
       <x:c r="AC3" s="15"/>
+      <x:c r="AD3" s="13"/>
+      <x:c r="AE3" s="15"/>
+      <x:c r="AF3" s="13"/>
+      <x:c r="AG3" s="15"/>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
       <x:c r="A4" s="12"/>
@@ -514,10 +538,10 @@
       <x:c r="E4" s="14"/>
       <x:c r="F4" s="14"/>
       <x:c r="G4" s="14"/>
-      <x:c r="H4" s="13"/>
-      <x:c r="I4" s="15"/>
-      <x:c r="J4" s="13"/>
-      <x:c r="K4" s="15"/>
+      <x:c r="H4" s="14"/>
+      <x:c r="I4" s="14"/>
+      <x:c r="J4" s="14"/>
+      <x:c r="K4" s="14"/>
       <x:c r="L4" s="13"/>
       <x:c r="M4" s="15"/>
       <x:c r="N4" s="13"/>
@@ -536,6 +560,10 @@
       <x:c r="AA4" s="15"/>
       <x:c r="AB4" s="13"/>
       <x:c r="AC4" s="15"/>
+      <x:c r="AD4" s="13"/>
+      <x:c r="AE4" s="15"/>
+      <x:c r="AF4" s="13"/>
+      <x:c r="AG4" s="15"/>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" s="12"/>
@@ -545,10 +573,10 @@
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14"/>
       <x:c r="G5" s="14"/>
-      <x:c r="H5" s="13"/>
-      <x:c r="I5" s="15"/>
-      <x:c r="J5" s="13"/>
-      <x:c r="K5" s="15"/>
+      <x:c r="H5" s="14"/>
+      <x:c r="I5" s="14"/>
+      <x:c r="J5" s="14"/>
+      <x:c r="K5" s="14"/>
       <x:c r="L5" s="13"/>
       <x:c r="M5" s="15"/>
       <x:c r="N5" s="13"/>
@@ -567,6 +595,10 @@
       <x:c r="AA5" s="15"/>
       <x:c r="AB5" s="13"/>
       <x:c r="AC5" s="15"/>
+      <x:c r="AD5" s="13"/>
+      <x:c r="AE5" s="15"/>
+      <x:c r="AF5" s="13"/>
+      <x:c r="AG5" s="15"/>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="12"/>
@@ -576,10 +608,10 @@
       <x:c r="E6" s="14"/>
       <x:c r="F6" s="14"/>
       <x:c r="G6" s="14"/>
-      <x:c r="H6" s="13"/>
-      <x:c r="I6" s="15"/>
-      <x:c r="J6" s="13"/>
-      <x:c r="K6" s="15"/>
+      <x:c r="H6" s="14"/>
+      <x:c r="I6" s="14"/>
+      <x:c r="J6" s="14"/>
+      <x:c r="K6" s="14"/>
       <x:c r="L6" s="13"/>
       <x:c r="M6" s="15"/>
       <x:c r="N6" s="13"/>
@@ -598,6 +630,10 @@
       <x:c r="AA6" s="15"/>
       <x:c r="AB6" s="13"/>
       <x:c r="AC6" s="15"/>
+      <x:c r="AD6" s="13"/>
+      <x:c r="AE6" s="15"/>
+      <x:c r="AF6" s="13"/>
+      <x:c r="AG6" s="15"/>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="12"/>
@@ -607,10 +643,10 @@
       <x:c r="E7" s="14"/>
       <x:c r="F7" s="14"/>
       <x:c r="G7" s="14"/>
-      <x:c r="H7" s="13"/>
-      <x:c r="I7" s="15"/>
-      <x:c r="J7" s="13"/>
-      <x:c r="K7" s="15"/>
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="14"/>
+      <x:c r="J7" s="14"/>
+      <x:c r="K7" s="14"/>
       <x:c r="L7" s="13"/>
       <x:c r="M7" s="15"/>
       <x:c r="N7" s="13"/>
@@ -629,6 +665,10 @@
       <x:c r="AA7" s="15"/>
       <x:c r="AB7" s="13"/>
       <x:c r="AC7" s="15"/>
+      <x:c r="AD7" s="13"/>
+      <x:c r="AE7" s="15"/>
+      <x:c r="AF7" s="13"/>
+      <x:c r="AG7" s="15"/>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
       <x:c r="A8" s="12"/>
@@ -638,10 +678,10 @@
       <x:c r="E8" s="14"/>
       <x:c r="F8" s="14"/>
       <x:c r="G8" s="14"/>
-      <x:c r="H8" s="13"/>
-      <x:c r="I8" s="15"/>
-      <x:c r="J8" s="13"/>
-      <x:c r="K8" s="15"/>
+      <x:c r="H8" s="14"/>
+      <x:c r="I8" s="14"/>
+      <x:c r="J8" s="14"/>
+      <x:c r="K8" s="14"/>
       <x:c r="L8" s="13"/>
       <x:c r="M8" s="15"/>
       <x:c r="N8" s="13"/>
@@ -660,6 +700,10 @@
       <x:c r="AA8" s="15"/>
       <x:c r="AB8" s="13"/>
       <x:c r="AC8" s="15"/>
+      <x:c r="AD8" s="13"/>
+      <x:c r="AE8" s="15"/>
+      <x:c r="AF8" s="13"/>
+      <x:c r="AG8" s="15"/>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
       <x:c r="A9" s="12"/>
@@ -669,10 +713,10 @@
       <x:c r="E9" s="14"/>
       <x:c r="F9" s="14"/>
       <x:c r="G9" s="14"/>
-      <x:c r="H9" s="13"/>
-      <x:c r="I9" s="15"/>
-      <x:c r="J9" s="13"/>
-      <x:c r="K9" s="15"/>
+      <x:c r="H9" s="14"/>
+      <x:c r="I9" s="14"/>
+      <x:c r="J9" s="14"/>
+      <x:c r="K9" s="14"/>
       <x:c r="L9" s="13"/>
       <x:c r="M9" s="15"/>
       <x:c r="N9" s="13"/>
@@ -691,6 +735,10 @@
       <x:c r="AA9" s="15"/>
       <x:c r="AB9" s="13"/>
       <x:c r="AC9" s="15"/>
+      <x:c r="AD9" s="13"/>
+      <x:c r="AE9" s="15"/>
+      <x:c r="AF9" s="13"/>
+      <x:c r="AG9" s="15"/>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
       <x:c r="A10" s="12"/>
@@ -700,10 +748,10 @@
       <x:c r="E10" s="14"/>
       <x:c r="F10" s="14"/>
       <x:c r="G10" s="14"/>
-      <x:c r="H10" s="13"/>
-      <x:c r="I10" s="15"/>
-      <x:c r="J10" s="13"/>
-      <x:c r="K10" s="15"/>
+      <x:c r="H10" s="14"/>
+      <x:c r="I10" s="14"/>
+      <x:c r="J10" s="14"/>
+      <x:c r="K10" s="14"/>
       <x:c r="L10" s="13"/>
       <x:c r="M10" s="15"/>
       <x:c r="N10" s="13"/>
@@ -722,6 +770,10 @@
       <x:c r="AA10" s="15"/>
       <x:c r="AB10" s="13"/>
       <x:c r="AC10" s="15"/>
+      <x:c r="AD10" s="13"/>
+      <x:c r="AE10" s="15"/>
+      <x:c r="AF10" s="13"/>
+      <x:c r="AG10" s="15"/>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
       <x:c r="A11" s="12"/>
@@ -731,10 +783,10 @@
       <x:c r="E11" s="14"/>
       <x:c r="F11" s="14"/>
       <x:c r="G11" s="14"/>
-      <x:c r="H11" s="13"/>
-      <x:c r="I11" s="15"/>
-      <x:c r="J11" s="13"/>
-      <x:c r="K11" s="15"/>
+      <x:c r="H11" s="14"/>
+      <x:c r="I11" s="14"/>
+      <x:c r="J11" s="14"/>
+      <x:c r="K11" s="14"/>
       <x:c r="L11" s="13"/>
       <x:c r="M11" s="15"/>
       <x:c r="N11" s="13"/>
@@ -753,6 +805,10 @@
       <x:c r="AA11" s="15"/>
       <x:c r="AB11" s="13"/>
       <x:c r="AC11" s="15"/>
+      <x:c r="AD11" s="13"/>
+      <x:c r="AE11" s="15"/>
+      <x:c r="AF11" s="13"/>
+      <x:c r="AG11" s="15"/>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
       <x:c r="A12" s="12"/>
@@ -762,10 +818,10 @@
       <x:c r="E12" s="14"/>
       <x:c r="F12" s="14"/>
       <x:c r="G12" s="14"/>
-      <x:c r="H12" s="13"/>
-      <x:c r="I12" s="15"/>
-      <x:c r="J12" s="13"/>
-      <x:c r="K12" s="15"/>
+      <x:c r="H12" s="14"/>
+      <x:c r="I12" s="14"/>
+      <x:c r="J12" s="14"/>
+      <x:c r="K12" s="14"/>
       <x:c r="L12" s="13"/>
       <x:c r="M12" s="15"/>
       <x:c r="N12" s="13"/>
@@ -784,6 +840,10 @@
       <x:c r="AA12" s="15"/>
       <x:c r="AB12" s="13"/>
       <x:c r="AC12" s="15"/>
+      <x:c r="AD12" s="13"/>
+      <x:c r="AE12" s="15"/>
+      <x:c r="AF12" s="13"/>
+      <x:c r="AG12" s="15"/>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" s="12"/>
@@ -793,10 +853,10 @@
       <x:c r="E13" s="14"/>
       <x:c r="F13" s="14"/>
       <x:c r="G13" s="14"/>
-      <x:c r="H13" s="13"/>
-      <x:c r="I13" s="15"/>
-      <x:c r="J13" s="13"/>
-      <x:c r="K13" s="15"/>
+      <x:c r="H13" s="14"/>
+      <x:c r="I13" s="14"/>
+      <x:c r="J13" s="14"/>
+      <x:c r="K13" s="14"/>
       <x:c r="L13" s="13"/>
       <x:c r="M13" s="15"/>
       <x:c r="N13" s="13"/>
@@ -815,6 +875,10 @@
       <x:c r="AA13" s="15"/>
       <x:c r="AB13" s="13"/>
       <x:c r="AC13" s="15"/>
+      <x:c r="AD13" s="13"/>
+      <x:c r="AE13" s="15"/>
+      <x:c r="AF13" s="13"/>
+      <x:c r="AG13" s="15"/>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
       <x:c r="A14" s="12"/>
@@ -824,10 +888,10 @@
       <x:c r="E14" s="14"/>
       <x:c r="F14" s="14"/>
       <x:c r="G14" s="14"/>
-      <x:c r="H14" s="13"/>
-      <x:c r="I14" s="15"/>
-      <x:c r="J14" s="13"/>
-      <x:c r="K14" s="15"/>
+      <x:c r="H14" s="14"/>
+      <x:c r="I14" s="14"/>
+      <x:c r="J14" s="14"/>
+      <x:c r="K14" s="14"/>
       <x:c r="L14" s="13"/>
       <x:c r="M14" s="15"/>
       <x:c r="N14" s="13"/>
@@ -846,6 +910,10 @@
       <x:c r="AA14" s="15"/>
       <x:c r="AB14" s="13"/>
       <x:c r="AC14" s="15"/>
+      <x:c r="AD14" s="13"/>
+      <x:c r="AE14" s="15"/>
+      <x:c r="AF14" s="13"/>
+      <x:c r="AG14" s="15"/>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" s="12"/>
@@ -855,10 +923,10 @@
       <x:c r="E15" s="14"/>
       <x:c r="F15" s="14"/>
       <x:c r="G15" s="14"/>
-      <x:c r="H15" s="13"/>
-      <x:c r="I15" s="15"/>
-      <x:c r="J15" s="13"/>
-      <x:c r="K15" s="15"/>
+      <x:c r="H15" s="14"/>
+      <x:c r="I15" s="14"/>
+      <x:c r="J15" s="14"/>
+      <x:c r="K15" s="14"/>
       <x:c r="L15" s="13"/>
       <x:c r="M15" s="15"/>
       <x:c r="N15" s="13"/>
@@ -877,6 +945,10 @@
       <x:c r="AA15" s="15"/>
       <x:c r="AB15" s="13"/>
       <x:c r="AC15" s="15"/>
+      <x:c r="AD15" s="13"/>
+      <x:c r="AE15" s="15"/>
+      <x:c r="AF15" s="13"/>
+      <x:c r="AG15" s="15"/>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
       <x:c r="A16" s="12"/>
@@ -886,10 +958,10 @@
       <x:c r="E16" s="14"/>
       <x:c r="F16" s="14"/>
       <x:c r="G16" s="14"/>
-      <x:c r="H16" s="13"/>
-      <x:c r="I16" s="15"/>
-      <x:c r="J16" s="13"/>
-      <x:c r="K16" s="15"/>
+      <x:c r="H16" s="14"/>
+      <x:c r="I16" s="14"/>
+      <x:c r="J16" s="14"/>
+      <x:c r="K16" s="14"/>
       <x:c r="L16" s="13"/>
       <x:c r="M16" s="15"/>
       <x:c r="N16" s="13"/>
@@ -908,6 +980,10 @@
       <x:c r="AA16" s="15"/>
       <x:c r="AB16" s="13"/>
       <x:c r="AC16" s="15"/>
+      <x:c r="AD16" s="13"/>
+      <x:c r="AE16" s="15"/>
+      <x:c r="AF16" s="13"/>
+      <x:c r="AG16" s="15"/>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
       <x:c r="A17" s="12"/>
@@ -917,10 +993,10 @@
       <x:c r="E17" s="14"/>
       <x:c r="F17" s="14"/>
       <x:c r="G17" s="14"/>
-      <x:c r="H17" s="13"/>
-      <x:c r="I17" s="15"/>
-      <x:c r="J17" s="13"/>
-      <x:c r="K17" s="15"/>
+      <x:c r="H17" s="14"/>
+      <x:c r="I17" s="14"/>
+      <x:c r="J17" s="14"/>
+      <x:c r="K17" s="14"/>
       <x:c r="L17" s="13"/>
       <x:c r="M17" s="15"/>
       <x:c r="N17" s="13"/>
@@ -939,6 +1015,10 @@
       <x:c r="AA17" s="15"/>
       <x:c r="AB17" s="13"/>
       <x:c r="AC17" s="15"/>
+      <x:c r="AD17" s="13"/>
+      <x:c r="AE17" s="15"/>
+      <x:c r="AF17" s="13"/>
+      <x:c r="AG17" s="15"/>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
       <x:c r="A18" s="12"/>
@@ -948,10 +1028,10 @@
       <x:c r="E18" s="14"/>
       <x:c r="F18" s="14"/>
       <x:c r="G18" s="14"/>
-      <x:c r="H18" s="13"/>
-      <x:c r="I18" s="15"/>
-      <x:c r="J18" s="13"/>
-      <x:c r="K18" s="15"/>
+      <x:c r="H18" s="14"/>
+      <x:c r="I18" s="14"/>
+      <x:c r="J18" s="14"/>
+      <x:c r="K18" s="14"/>
       <x:c r="L18" s="13"/>
       <x:c r="M18" s="15"/>
       <x:c r="N18" s="13"/>
@@ -970,6 +1050,10 @@
       <x:c r="AA18" s="15"/>
       <x:c r="AB18" s="13"/>
       <x:c r="AC18" s="15"/>
+      <x:c r="AD18" s="13"/>
+      <x:c r="AE18" s="15"/>
+      <x:c r="AF18" s="13"/>
+      <x:c r="AG18" s="15"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="12"/>
@@ -979,10 +1063,10 @@
       <x:c r="E19" s="14"/>
       <x:c r="F19" s="14"/>
       <x:c r="G19" s="14"/>
-      <x:c r="H19" s="13"/>
-      <x:c r="I19" s="15"/>
-      <x:c r="J19" s="13"/>
-      <x:c r="K19" s="15"/>
+      <x:c r="H19" s="14"/>
+      <x:c r="I19" s="14"/>
+      <x:c r="J19" s="14"/>
+      <x:c r="K19" s="14"/>
       <x:c r="L19" s="13"/>
       <x:c r="M19" s="15"/>
       <x:c r="N19" s="13"/>
@@ -1001,6 +1085,10 @@
       <x:c r="AA19" s="15"/>
       <x:c r="AB19" s="13"/>
       <x:c r="AC19" s="15"/>
+      <x:c r="AD19" s="13"/>
+      <x:c r="AE19" s="15"/>
+      <x:c r="AF19" s="13"/>
+      <x:c r="AG19" s="15"/>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
       <x:c r="A20" s="12"/>
@@ -1010,10 +1098,10 @@
       <x:c r="E20" s="14"/>
       <x:c r="F20" s="14"/>
       <x:c r="G20" s="14"/>
-      <x:c r="H20" s="13"/>
-      <x:c r="I20" s="15"/>
-      <x:c r="J20" s="13"/>
-      <x:c r="K20" s="15"/>
+      <x:c r="H20" s="14"/>
+      <x:c r="I20" s="14"/>
+      <x:c r="J20" s="14"/>
+      <x:c r="K20" s="14"/>
       <x:c r="L20" s="13"/>
       <x:c r="M20" s="15"/>
       <x:c r="N20" s="13"/>
@@ -1032,6 +1120,10 @@
       <x:c r="AA20" s="15"/>
       <x:c r="AB20" s="13"/>
       <x:c r="AC20" s="15"/>
+      <x:c r="AD20" s="13"/>
+      <x:c r="AE20" s="15"/>
+      <x:c r="AF20" s="13"/>
+      <x:c r="AG20" s="15"/>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
       <x:c r="A21" s="12"/>
@@ -1041,10 +1133,10 @@
       <x:c r="E21" s="14"/>
       <x:c r="F21" s="14"/>
       <x:c r="G21" s="14"/>
-      <x:c r="H21" s="13"/>
-      <x:c r="I21" s="15"/>
-      <x:c r="J21" s="13"/>
-      <x:c r="K21" s="15"/>
+      <x:c r="H21" s="14"/>
+      <x:c r="I21" s="14"/>
+      <x:c r="J21" s="14"/>
+      <x:c r="K21" s="14"/>
       <x:c r="L21" s="13"/>
       <x:c r="M21" s="15"/>
       <x:c r="N21" s="13"/>
@@ -1063,6 +1155,10 @@
       <x:c r="AA21" s="15"/>
       <x:c r="AB21" s="13"/>
       <x:c r="AC21" s="15"/>
+      <x:c r="AD21" s="13"/>
+      <x:c r="AE21" s="15"/>
+      <x:c r="AF21" s="13"/>
+      <x:c r="AG21" s="15"/>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
       <x:c r="A22" s="12"/>
@@ -1072,10 +1168,10 @@
       <x:c r="E22" s="14"/>
       <x:c r="F22" s="14"/>
       <x:c r="G22" s="14"/>
-      <x:c r="H22" s="13"/>
-      <x:c r="I22" s="15"/>
-      <x:c r="J22" s="13"/>
-      <x:c r="K22" s="15"/>
+      <x:c r="H22" s="14"/>
+      <x:c r="I22" s="14"/>
+      <x:c r="J22" s="14"/>
+      <x:c r="K22" s="14"/>
       <x:c r="L22" s="13"/>
       <x:c r="M22" s="15"/>
       <x:c r="N22" s="13"/>
@@ -1094,6 +1190,10 @@
       <x:c r="AA22" s="15"/>
       <x:c r="AB22" s="13"/>
       <x:c r="AC22" s="15"/>
+      <x:c r="AD22" s="13"/>
+      <x:c r="AE22" s="15"/>
+      <x:c r="AF22" s="13"/>
+      <x:c r="AG22" s="15"/>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="12"/>
@@ -1103,10 +1203,10 @@
       <x:c r="E23" s="14"/>
       <x:c r="F23" s="14"/>
       <x:c r="G23" s="14"/>
-      <x:c r="H23" s="13"/>
-      <x:c r="I23" s="15"/>
-      <x:c r="J23" s="13"/>
-      <x:c r="K23" s="15"/>
+      <x:c r="H23" s="14"/>
+      <x:c r="I23" s="14"/>
+      <x:c r="J23" s="14"/>
+      <x:c r="K23" s="14"/>
       <x:c r="L23" s="13"/>
       <x:c r="M23" s="15"/>
       <x:c r="N23" s="13"/>
@@ -1125,6 +1225,10 @@
       <x:c r="AA23" s="15"/>
       <x:c r="AB23" s="13"/>
       <x:c r="AC23" s="15"/>
+      <x:c r="AD23" s="13"/>
+      <x:c r="AE23" s="15"/>
+      <x:c r="AF23" s="13"/>
+      <x:c r="AG23" s="15"/>
     </x:row>
     <x:row r="24" ht="25" customHeight="1">
       <x:c r="A24" s="12"/>
@@ -1134,10 +1238,10 @@
       <x:c r="E24" s="14"/>
       <x:c r="F24" s="14"/>
       <x:c r="G24" s="14"/>
-      <x:c r="H24" s="13"/>
-      <x:c r="I24" s="15"/>
-      <x:c r="J24" s="13"/>
-      <x:c r="K24" s="15"/>
+      <x:c r="H24" s="14"/>
+      <x:c r="I24" s="14"/>
+      <x:c r="J24" s="14"/>
+      <x:c r="K24" s="14"/>
       <x:c r="L24" s="13"/>
       <x:c r="M24" s="15"/>
       <x:c r="N24" s="13"/>
@@ -1156,6 +1260,10 @@
       <x:c r="AA24" s="15"/>
       <x:c r="AB24" s="13"/>
       <x:c r="AC24" s="15"/>
+      <x:c r="AD24" s="13"/>
+      <x:c r="AE24" s="15"/>
+      <x:c r="AF24" s="13"/>
+      <x:c r="AG24" s="15"/>
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="12"/>
@@ -1165,10 +1273,10 @@
       <x:c r="E25" s="14"/>
       <x:c r="F25" s="14"/>
       <x:c r="G25" s="14"/>
-      <x:c r="H25" s="13"/>
-      <x:c r="I25" s="15"/>
-      <x:c r="J25" s="13"/>
-      <x:c r="K25" s="15"/>
+      <x:c r="H25" s="14"/>
+      <x:c r="I25" s="14"/>
+      <x:c r="J25" s="14"/>
+      <x:c r="K25" s="14"/>
       <x:c r="L25" s="13"/>
       <x:c r="M25" s="15"/>
       <x:c r="N25" s="13"/>
@@ -1187,6 +1295,10 @@
       <x:c r="AA25" s="15"/>
       <x:c r="AB25" s="13"/>
       <x:c r="AC25" s="15"/>
+      <x:c r="AD25" s="13"/>
+      <x:c r="AE25" s="15"/>
+      <x:c r="AF25" s="13"/>
+      <x:c r="AG25" s="15"/>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="12"/>
@@ -1196,10 +1308,10 @@
       <x:c r="E26" s="14"/>
       <x:c r="F26" s="14"/>
       <x:c r="G26" s="14"/>
-      <x:c r="H26" s="13"/>
-      <x:c r="I26" s="15"/>
-      <x:c r="J26" s="13"/>
-      <x:c r="K26" s="15"/>
+      <x:c r="H26" s="14"/>
+      <x:c r="I26" s="14"/>
+      <x:c r="J26" s="14"/>
+      <x:c r="K26" s="14"/>
       <x:c r="L26" s="13"/>
       <x:c r="M26" s="15"/>
       <x:c r="N26" s="13"/>
@@ -1218,6 +1330,10 @@
       <x:c r="AA26" s="15"/>
       <x:c r="AB26" s="13"/>
       <x:c r="AC26" s="15"/>
+      <x:c r="AD26" s="13"/>
+      <x:c r="AE26" s="15"/>
+      <x:c r="AF26" s="13"/>
+      <x:c r="AG26" s="15"/>
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="12"/>
@@ -1227,10 +1343,10 @@
       <x:c r="E27" s="14"/>
       <x:c r="F27" s="14"/>
       <x:c r="G27" s="14"/>
-      <x:c r="H27" s="13"/>
-      <x:c r="I27" s="15"/>
-      <x:c r="J27" s="13"/>
-      <x:c r="K27" s="15"/>
+      <x:c r="H27" s="14"/>
+      <x:c r="I27" s="14"/>
+      <x:c r="J27" s="14"/>
+      <x:c r="K27" s="14"/>
       <x:c r="L27" s="13"/>
       <x:c r="M27" s="15"/>
       <x:c r="N27" s="13"/>
@@ -1249,6 +1365,10 @@
       <x:c r="AA27" s="15"/>
       <x:c r="AB27" s="13"/>
       <x:c r="AC27" s="15"/>
+      <x:c r="AD27" s="13"/>
+      <x:c r="AE27" s="15"/>
+      <x:c r="AF27" s="13"/>
+      <x:c r="AG27" s="15"/>
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="12"/>
@@ -1258,10 +1378,10 @@
       <x:c r="E28" s="14"/>
       <x:c r="F28" s="14"/>
       <x:c r="G28" s="14"/>
-      <x:c r="H28" s="13"/>
-      <x:c r="I28" s="15"/>
-      <x:c r="J28" s="13"/>
-      <x:c r="K28" s="15"/>
+      <x:c r="H28" s="14"/>
+      <x:c r="I28" s="14"/>
+      <x:c r="J28" s="14"/>
+      <x:c r="K28" s="14"/>
       <x:c r="L28" s="13"/>
       <x:c r="M28" s="15"/>
       <x:c r="N28" s="13"/>
@@ -1280,6 +1400,10 @@
       <x:c r="AA28" s="15"/>
       <x:c r="AB28" s="13"/>
       <x:c r="AC28" s="15"/>
+      <x:c r="AD28" s="13"/>
+      <x:c r="AE28" s="15"/>
+      <x:c r="AF28" s="13"/>
+      <x:c r="AG28" s="15"/>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="12"/>
@@ -1289,10 +1413,10 @@
       <x:c r="E29" s="14"/>
       <x:c r="F29" s="14"/>
       <x:c r="G29" s="14"/>
-      <x:c r="H29" s="13"/>
-      <x:c r="I29" s="15"/>
-      <x:c r="J29" s="13"/>
-      <x:c r="K29" s="15"/>
+      <x:c r="H29" s="14"/>
+      <x:c r="I29" s="14"/>
+      <x:c r="J29" s="14"/>
+      <x:c r="K29" s="14"/>
       <x:c r="L29" s="13"/>
       <x:c r="M29" s="15"/>
       <x:c r="N29" s="13"/>
@@ -1311,6 +1435,10 @@
       <x:c r="AA29" s="15"/>
       <x:c r="AB29" s="13"/>
       <x:c r="AC29" s="15"/>
+      <x:c r="AD29" s="13"/>
+      <x:c r="AE29" s="15"/>
+      <x:c r="AF29" s="13"/>
+      <x:c r="AG29" s="15"/>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="12"/>
@@ -1320,10 +1448,10 @@
       <x:c r="E30" s="14"/>
       <x:c r="F30" s="14"/>
       <x:c r="G30" s="14"/>
-      <x:c r="H30" s="13"/>
-      <x:c r="I30" s="15"/>
-      <x:c r="J30" s="13"/>
-      <x:c r="K30" s="15"/>
+      <x:c r="H30" s="14"/>
+      <x:c r="I30" s="14"/>
+      <x:c r="J30" s="14"/>
+      <x:c r="K30" s="14"/>
       <x:c r="L30" s="13"/>
       <x:c r="M30" s="15"/>
       <x:c r="N30" s="13"/>
@@ -1342,6 +1470,10 @@
       <x:c r="AA30" s="15"/>
       <x:c r="AB30" s="13"/>
       <x:c r="AC30" s="15"/>
+      <x:c r="AD30" s="13"/>
+      <x:c r="AE30" s="15"/>
+      <x:c r="AF30" s="13"/>
+      <x:c r="AG30" s="15"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="12"/>
@@ -1351,10 +1483,10 @@
       <x:c r="E31" s="14"/>
       <x:c r="F31" s="14"/>
       <x:c r="G31" s="14"/>
-      <x:c r="H31" s="13"/>
-      <x:c r="I31" s="15"/>
-      <x:c r="J31" s="13"/>
-      <x:c r="K31" s="15"/>
+      <x:c r="H31" s="14"/>
+      <x:c r="I31" s="14"/>
+      <x:c r="J31" s="14"/>
+      <x:c r="K31" s="14"/>
       <x:c r="L31" s="13"/>
       <x:c r="M31" s="15"/>
       <x:c r="N31" s="13"/>
@@ -1373,6 +1505,10 @@
       <x:c r="AA31" s="15"/>
       <x:c r="AB31" s="13"/>
       <x:c r="AC31" s="15"/>
+      <x:c r="AD31" s="13"/>
+      <x:c r="AE31" s="15"/>
+      <x:c r="AF31" s="13"/>
+      <x:c r="AG31" s="15"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="12"/>
@@ -1382,10 +1518,10 @@
       <x:c r="E32" s="14"/>
       <x:c r="F32" s="14"/>
       <x:c r="G32" s="14"/>
-      <x:c r="H32" s="13"/>
-      <x:c r="I32" s="15"/>
-      <x:c r="J32" s="13"/>
-      <x:c r="K32" s="15"/>
+      <x:c r="H32" s="14"/>
+      <x:c r="I32" s="14"/>
+      <x:c r="J32" s="14"/>
+      <x:c r="K32" s="14"/>
       <x:c r="L32" s="13"/>
       <x:c r="M32" s="15"/>
       <x:c r="N32" s="13"/>
@@ -1404,6 +1540,10 @@
       <x:c r="AA32" s="15"/>
       <x:c r="AB32" s="13"/>
       <x:c r="AC32" s="15"/>
+      <x:c r="AD32" s="13"/>
+      <x:c r="AE32" s="15"/>
+      <x:c r="AF32" s="13"/>
+      <x:c r="AG32" s="15"/>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
       <x:c r="A33" s="12"/>
@@ -1413,10 +1553,10 @@
       <x:c r="E33" s="14"/>
       <x:c r="F33" s="14"/>
       <x:c r="G33" s="14"/>
-      <x:c r="H33" s="13"/>
-      <x:c r="I33" s="15"/>
-      <x:c r="J33" s="13"/>
-      <x:c r="K33" s="15"/>
+      <x:c r="H33" s="14"/>
+      <x:c r="I33" s="14"/>
+      <x:c r="J33" s="14"/>
+      <x:c r="K33" s="14"/>
       <x:c r="L33" s="13"/>
       <x:c r="M33" s="15"/>
       <x:c r="N33" s="13"/>
@@ -1435,6 +1575,10 @@
       <x:c r="AA33" s="15"/>
       <x:c r="AB33" s="13"/>
       <x:c r="AC33" s="15"/>
+      <x:c r="AD33" s="13"/>
+      <x:c r="AE33" s="15"/>
+      <x:c r="AF33" s="13"/>
+      <x:c r="AG33" s="15"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="12"/>
@@ -1444,10 +1588,10 @@
       <x:c r="E34" s="14"/>
       <x:c r="F34" s="14"/>
       <x:c r="G34" s="14"/>
-      <x:c r="H34" s="13"/>
-      <x:c r="I34" s="15"/>
-      <x:c r="J34" s="13"/>
-      <x:c r="K34" s="15"/>
+      <x:c r="H34" s="14"/>
+      <x:c r="I34" s="14"/>
+      <x:c r="J34" s="14"/>
+      <x:c r="K34" s="14"/>
       <x:c r="L34" s="13"/>
       <x:c r="M34" s="15"/>
       <x:c r="N34" s="13"/>
@@ -1466,6 +1610,10 @@
       <x:c r="AA34" s="15"/>
       <x:c r="AB34" s="13"/>
       <x:c r="AC34" s="15"/>
+      <x:c r="AD34" s="13"/>
+      <x:c r="AE34" s="15"/>
+      <x:c r="AF34" s="13"/>
+      <x:c r="AG34" s="15"/>
     </x:row>
     <x:row r="35" ht="25" customHeight="1">
       <x:c r="A35" s="12"/>
@@ -1475,10 +1623,10 @@
       <x:c r="E35" s="14"/>
       <x:c r="F35" s="14"/>
       <x:c r="G35" s="14"/>
-      <x:c r="H35" s="13"/>
-      <x:c r="I35" s="15"/>
-      <x:c r="J35" s="13"/>
-      <x:c r="K35" s="15"/>
+      <x:c r="H35" s="14"/>
+      <x:c r="I35" s="14"/>
+      <x:c r="J35" s="14"/>
+      <x:c r="K35" s="14"/>
       <x:c r="L35" s="13"/>
       <x:c r="M35" s="15"/>
       <x:c r="N35" s="13"/>
@@ -1497,6 +1645,10 @@
       <x:c r="AA35" s="15"/>
       <x:c r="AB35" s="13"/>
       <x:c r="AC35" s="15"/>
+      <x:c r="AD35" s="13"/>
+      <x:c r="AE35" s="15"/>
+      <x:c r="AF35" s="13"/>
+      <x:c r="AG35" s="15"/>
     </x:row>
     <x:row r="36" ht="25" customHeight="1">
       <x:c r="A36" s="12"/>
@@ -1506,10 +1658,10 @@
       <x:c r="E36" s="14"/>
       <x:c r="F36" s="14"/>
       <x:c r="G36" s="14"/>
-      <x:c r="H36" s="13"/>
-      <x:c r="I36" s="15"/>
-      <x:c r="J36" s="13"/>
-      <x:c r="K36" s="15"/>
+      <x:c r="H36" s="14"/>
+      <x:c r="I36" s="14"/>
+      <x:c r="J36" s="14"/>
+      <x:c r="K36" s="14"/>
       <x:c r="L36" s="13"/>
       <x:c r="M36" s="15"/>
       <x:c r="N36" s="13"/>
@@ -1528,6 +1680,10 @@
       <x:c r="AA36" s="15"/>
       <x:c r="AB36" s="13"/>
       <x:c r="AC36" s="15"/>
+      <x:c r="AD36" s="13"/>
+      <x:c r="AE36" s="15"/>
+      <x:c r="AF36" s="13"/>
+      <x:c r="AG36" s="15"/>
     </x:row>
     <x:row r="37" ht="25" customHeight="1">
       <x:c r="A37" s="12"/>
@@ -1537,10 +1693,10 @@
       <x:c r="E37" s="14"/>
       <x:c r="F37" s="14"/>
       <x:c r="G37" s="14"/>
-      <x:c r="H37" s="13"/>
-      <x:c r="I37" s="15"/>
-      <x:c r="J37" s="13"/>
-      <x:c r="K37" s="15"/>
+      <x:c r="H37" s="14"/>
+      <x:c r="I37" s="14"/>
+      <x:c r="J37" s="14"/>
+      <x:c r="K37" s="14"/>
       <x:c r="L37" s="13"/>
       <x:c r="M37" s="15"/>
       <x:c r="N37" s="13"/>
@@ -1559,6 +1715,10 @@
       <x:c r="AA37" s="15"/>
       <x:c r="AB37" s="13"/>
       <x:c r="AC37" s="15"/>
+      <x:c r="AD37" s="13"/>
+      <x:c r="AE37" s="15"/>
+      <x:c r="AF37" s="13"/>
+      <x:c r="AG37" s="15"/>
     </x:row>
     <x:row r="38" ht="25" customHeight="1">
       <x:c r="A38" s="12"/>
@@ -1568,10 +1728,10 @@
       <x:c r="E38" s="14"/>
       <x:c r="F38" s="14"/>
       <x:c r="G38" s="14"/>
-      <x:c r="H38" s="13"/>
-      <x:c r="I38" s="15"/>
-      <x:c r="J38" s="13"/>
-      <x:c r="K38" s="15"/>
+      <x:c r="H38" s="14"/>
+      <x:c r="I38" s="14"/>
+      <x:c r="J38" s="14"/>
+      <x:c r="K38" s="14"/>
       <x:c r="L38" s="13"/>
       <x:c r="M38" s="15"/>
       <x:c r="N38" s="13"/>
@@ -1590,6 +1750,10 @@
       <x:c r="AA38" s="15"/>
       <x:c r="AB38" s="13"/>
       <x:c r="AC38" s="15"/>
+      <x:c r="AD38" s="13"/>
+      <x:c r="AE38" s="15"/>
+      <x:c r="AF38" s="13"/>
+      <x:c r="AG38" s="15"/>
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
       <x:c r="A39" s="12"/>
@@ -1599,10 +1763,10 @@
       <x:c r="E39" s="14"/>
       <x:c r="F39" s="14"/>
       <x:c r="G39" s="14"/>
-      <x:c r="H39" s="13"/>
-      <x:c r="I39" s="15"/>
-      <x:c r="J39" s="13"/>
-      <x:c r="K39" s="15"/>
+      <x:c r="H39" s="14"/>
+      <x:c r="I39" s="14"/>
+      <x:c r="J39" s="14"/>
+      <x:c r="K39" s="14"/>
       <x:c r="L39" s="13"/>
       <x:c r="M39" s="15"/>
       <x:c r="N39" s="13"/>
@@ -1621,6 +1785,10 @@
       <x:c r="AA39" s="15"/>
       <x:c r="AB39" s="13"/>
       <x:c r="AC39" s="15"/>
+      <x:c r="AD39" s="13"/>
+      <x:c r="AE39" s="15"/>
+      <x:c r="AF39" s="13"/>
+      <x:c r="AG39" s="15"/>
     </x:row>
     <x:row r="40" ht="25" customHeight="1">
       <x:c r="A40" s="12"/>
@@ -1630,10 +1798,10 @@
       <x:c r="E40" s="14"/>
       <x:c r="F40" s="14"/>
       <x:c r="G40" s="14"/>
-      <x:c r="H40" s="13"/>
-      <x:c r="I40" s="15"/>
-      <x:c r="J40" s="13"/>
-      <x:c r="K40" s="15"/>
+      <x:c r="H40" s="14"/>
+      <x:c r="I40" s="14"/>
+      <x:c r="J40" s="14"/>
+      <x:c r="K40" s="14"/>
       <x:c r="L40" s="13"/>
       <x:c r="M40" s="15"/>
       <x:c r="N40" s="13"/>
@@ -1652,6 +1820,10 @@
       <x:c r="AA40" s="15"/>
       <x:c r="AB40" s="13"/>
       <x:c r="AC40" s="15"/>
+      <x:c r="AD40" s="13"/>
+      <x:c r="AE40" s="15"/>
+      <x:c r="AF40" s="13"/>
+      <x:c r="AG40" s="15"/>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
       <x:c r="A41" s="12"/>
@@ -1661,10 +1833,10 @@
       <x:c r="E41" s="14"/>
       <x:c r="F41" s="14"/>
       <x:c r="G41" s="14"/>
-      <x:c r="H41" s="13"/>
-      <x:c r="I41" s="15"/>
-      <x:c r="J41" s="13"/>
-      <x:c r="K41" s="15"/>
+      <x:c r="H41" s="14"/>
+      <x:c r="I41" s="14"/>
+      <x:c r="J41" s="14"/>
+      <x:c r="K41" s="14"/>
       <x:c r="L41" s="13"/>
       <x:c r="M41" s="15"/>
       <x:c r="N41" s="13"/>
@@ -1683,6 +1855,10 @@
       <x:c r="AA41" s="15"/>
       <x:c r="AB41" s="13"/>
       <x:c r="AC41" s="15"/>
+      <x:c r="AD41" s="13"/>
+      <x:c r="AE41" s="15"/>
+      <x:c r="AF41" s="13"/>
+      <x:c r="AG41" s="15"/>
     </x:row>
     <x:row r="42" ht="25" customHeight="1">
       <x:c r="A42" s="12"/>
@@ -1692,10 +1868,10 @@
       <x:c r="E42" s="14"/>
       <x:c r="F42" s="14"/>
       <x:c r="G42" s="14"/>
-      <x:c r="H42" s="13"/>
-      <x:c r="I42" s="15"/>
-      <x:c r="J42" s="13"/>
-      <x:c r="K42" s="15"/>
+      <x:c r="H42" s="14"/>
+      <x:c r="I42" s="14"/>
+      <x:c r="J42" s="14"/>
+      <x:c r="K42" s="14"/>
       <x:c r="L42" s="13"/>
       <x:c r="M42" s="15"/>
       <x:c r="N42" s="13"/>
@@ -1714,6 +1890,10 @@
       <x:c r="AA42" s="15"/>
       <x:c r="AB42" s="13"/>
       <x:c r="AC42" s="15"/>
+      <x:c r="AD42" s="13"/>
+      <x:c r="AE42" s="15"/>
+      <x:c r="AF42" s="13"/>
+      <x:c r="AG42" s="15"/>
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
       <x:c r="A43" s="12"/>
@@ -1723,10 +1903,10 @@
       <x:c r="E43" s="14"/>
       <x:c r="F43" s="14"/>
       <x:c r="G43" s="14"/>
-      <x:c r="H43" s="13"/>
-      <x:c r="I43" s="15"/>
-      <x:c r="J43" s="13"/>
-      <x:c r="K43" s="15"/>
+      <x:c r="H43" s="14"/>
+      <x:c r="I43" s="14"/>
+      <x:c r="J43" s="14"/>
+      <x:c r="K43" s="14"/>
       <x:c r="L43" s="13"/>
       <x:c r="M43" s="15"/>
       <x:c r="N43" s="13"/>
@@ -1745,6 +1925,10 @@
       <x:c r="AA43" s="15"/>
       <x:c r="AB43" s="13"/>
       <x:c r="AC43" s="15"/>
+      <x:c r="AD43" s="13"/>
+      <x:c r="AE43" s="15"/>
+      <x:c r="AF43" s="13"/>
+      <x:c r="AG43" s="15"/>
     </x:row>
     <x:row r="44" ht="25" customHeight="1">
       <x:c r="A44" s="12"/>
@@ -1754,10 +1938,10 @@
       <x:c r="E44" s="14"/>
       <x:c r="F44" s="14"/>
       <x:c r="G44" s="14"/>
-      <x:c r="H44" s="13"/>
-      <x:c r="I44" s="15"/>
-      <x:c r="J44" s="13"/>
-      <x:c r="K44" s="15"/>
+      <x:c r="H44" s="14"/>
+      <x:c r="I44" s="14"/>
+      <x:c r="J44" s="14"/>
+      <x:c r="K44" s="14"/>
       <x:c r="L44" s="13"/>
       <x:c r="M44" s="15"/>
       <x:c r="N44" s="13"/>
@@ -1776,6 +1960,10 @@
       <x:c r="AA44" s="15"/>
       <x:c r="AB44" s="13"/>
       <x:c r="AC44" s="15"/>
+      <x:c r="AD44" s="13"/>
+      <x:c r="AE44" s="15"/>
+      <x:c r="AF44" s="13"/>
+      <x:c r="AG44" s="15"/>
     </x:row>
     <x:row r="45" ht="25" customHeight="1">
       <x:c r="A45" s="12"/>
@@ -1785,10 +1973,10 @@
       <x:c r="E45" s="14"/>
       <x:c r="F45" s="14"/>
       <x:c r="G45" s="14"/>
-      <x:c r="H45" s="13"/>
-      <x:c r="I45" s="15"/>
-      <x:c r="J45" s="13"/>
-      <x:c r="K45" s="15"/>
+      <x:c r="H45" s="14"/>
+      <x:c r="I45" s="14"/>
+      <x:c r="J45" s="14"/>
+      <x:c r="K45" s="14"/>
       <x:c r="L45" s="13"/>
       <x:c r="M45" s="15"/>
       <x:c r="N45" s="13"/>
@@ -1807,6 +1995,10 @@
       <x:c r="AA45" s="15"/>
       <x:c r="AB45" s="13"/>
       <x:c r="AC45" s="15"/>
+      <x:c r="AD45" s="13"/>
+      <x:c r="AE45" s="15"/>
+      <x:c r="AF45" s="13"/>
+      <x:c r="AG45" s="15"/>
     </x:row>
     <x:row r="46" ht="25" customHeight="1">
       <x:c r="A46" s="12"/>
@@ -1816,10 +2008,10 @@
       <x:c r="E46" s="14"/>
       <x:c r="F46" s="14"/>
       <x:c r="G46" s="14"/>
-      <x:c r="H46" s="13"/>
-      <x:c r="I46" s="15"/>
-      <x:c r="J46" s="13"/>
-      <x:c r="K46" s="15"/>
+      <x:c r="H46" s="14"/>
+      <x:c r="I46" s="14"/>
+      <x:c r="J46" s="14"/>
+      <x:c r="K46" s="14"/>
       <x:c r="L46" s="13"/>
       <x:c r="M46" s="15"/>
       <x:c r="N46" s="13"/>
@@ -1838,6 +2030,10 @@
       <x:c r="AA46" s="15"/>
       <x:c r="AB46" s="13"/>
       <x:c r="AC46" s="15"/>
+      <x:c r="AD46" s="13"/>
+      <x:c r="AE46" s="15"/>
+      <x:c r="AF46" s="13"/>
+      <x:c r="AG46" s="15"/>
     </x:row>
     <x:row r="47" ht="25" customHeight="1">
       <x:c r="A47" s="12"/>
@@ -1847,10 +2043,10 @@
       <x:c r="E47" s="14"/>
       <x:c r="F47" s="14"/>
       <x:c r="G47" s="14"/>
-      <x:c r="H47" s="13"/>
-      <x:c r="I47" s="15"/>
-      <x:c r="J47" s="13"/>
-      <x:c r="K47" s="15"/>
+      <x:c r="H47" s="14"/>
+      <x:c r="I47" s="14"/>
+      <x:c r="J47" s="14"/>
+      <x:c r="K47" s="14"/>
       <x:c r="L47" s="13"/>
       <x:c r="M47" s="15"/>
       <x:c r="N47" s="13"/>
@@ -1869,6 +2065,10 @@
       <x:c r="AA47" s="15"/>
       <x:c r="AB47" s="13"/>
       <x:c r="AC47" s="15"/>
+      <x:c r="AD47" s="13"/>
+      <x:c r="AE47" s="15"/>
+      <x:c r="AF47" s="13"/>
+      <x:c r="AG47" s="15"/>
     </x:row>
     <x:row r="48" ht="25" customHeight="1">
       <x:c r="A48" s="12"/>
@@ -1878,10 +2078,10 @@
       <x:c r="E48" s="14"/>
       <x:c r="F48" s="14"/>
       <x:c r="G48" s="14"/>
-      <x:c r="H48" s="13"/>
-      <x:c r="I48" s="15"/>
-      <x:c r="J48" s="13"/>
-      <x:c r="K48" s="15"/>
+      <x:c r="H48" s="14"/>
+      <x:c r="I48" s="14"/>
+      <x:c r="J48" s="14"/>
+      <x:c r="K48" s="14"/>
       <x:c r="L48" s="13"/>
       <x:c r="M48" s="15"/>
       <x:c r="N48" s="13"/>
@@ -1900,6 +2100,10 @@
       <x:c r="AA48" s="15"/>
       <x:c r="AB48" s="13"/>
       <x:c r="AC48" s="15"/>
+      <x:c r="AD48" s="13"/>
+      <x:c r="AE48" s="15"/>
+      <x:c r="AF48" s="13"/>
+      <x:c r="AG48" s="15"/>
     </x:row>
     <x:row r="49" ht="25" customHeight="1">
       <x:c r="A49" s="12"/>
@@ -1909,10 +2113,10 @@
       <x:c r="E49" s="14"/>
       <x:c r="F49" s="14"/>
       <x:c r="G49" s="14"/>
-      <x:c r="H49" s="13"/>
-      <x:c r="I49" s="15"/>
-      <x:c r="J49" s="13"/>
-      <x:c r="K49" s="15"/>
+      <x:c r="H49" s="14"/>
+      <x:c r="I49" s="14"/>
+      <x:c r="J49" s="14"/>
+      <x:c r="K49" s="14"/>
       <x:c r="L49" s="13"/>
       <x:c r="M49" s="15"/>
       <x:c r="N49" s="13"/>
@@ -1931,6 +2135,10 @@
       <x:c r="AA49" s="15"/>
       <x:c r="AB49" s="13"/>
       <x:c r="AC49" s="15"/>
+      <x:c r="AD49" s="13"/>
+      <x:c r="AE49" s="15"/>
+      <x:c r="AF49" s="13"/>
+      <x:c r="AG49" s="15"/>
     </x:row>
     <x:row r="50" ht="25" customHeight="1">
       <x:c r="A50" s="12"/>
@@ -1940,10 +2148,10 @@
       <x:c r="E50" s="14"/>
       <x:c r="F50" s="14"/>
       <x:c r="G50" s="14"/>
-      <x:c r="H50" s="13"/>
-      <x:c r="I50" s="15"/>
-      <x:c r="J50" s="13"/>
-      <x:c r="K50" s="15"/>
+      <x:c r="H50" s="14"/>
+      <x:c r="I50" s="14"/>
+      <x:c r="J50" s="14"/>
+      <x:c r="K50" s="14"/>
       <x:c r="L50" s="13"/>
       <x:c r="M50" s="15"/>
       <x:c r="N50" s="13"/>
@@ -1962,6 +2170,10 @@
       <x:c r="AA50" s="15"/>
       <x:c r="AB50" s="13"/>
       <x:c r="AC50" s="15"/>
+      <x:c r="AD50" s="13"/>
+      <x:c r="AE50" s="15"/>
+      <x:c r="AF50" s="13"/>
+      <x:c r="AG50" s="15"/>
     </x:row>
     <x:row r="51" ht="25" customHeight="1">
       <x:c r="A51" s="12"/>
@@ -1971,10 +2183,10 @@
       <x:c r="E51" s="14"/>
       <x:c r="F51" s="14"/>
       <x:c r="G51" s="14"/>
-      <x:c r="H51" s="13"/>
-      <x:c r="I51" s="15"/>
-      <x:c r="J51" s="13"/>
-      <x:c r="K51" s="15"/>
+      <x:c r="H51" s="14"/>
+      <x:c r="I51" s="14"/>
+      <x:c r="J51" s="14"/>
+      <x:c r="K51" s="14"/>
       <x:c r="L51" s="13"/>
       <x:c r="M51" s="15"/>
       <x:c r="N51" s="13"/>
@@ -1993,6 +2205,10 @@
       <x:c r="AA51" s="15"/>
       <x:c r="AB51" s="13"/>
       <x:c r="AC51" s="15"/>
+      <x:c r="AD51" s="13"/>
+      <x:c r="AE51" s="15"/>
+      <x:c r="AF51" s="13"/>
+      <x:c r="AG51" s="15"/>
     </x:row>
     <x:row r="52" ht="25" customHeight="1">
       <x:c r="A52" s="12"/>
@@ -2002,10 +2218,10 @@
       <x:c r="E52" s="14"/>
       <x:c r="F52" s="14"/>
       <x:c r="G52" s="14"/>
-      <x:c r="H52" s="13"/>
-      <x:c r="I52" s="15"/>
-      <x:c r="J52" s="13"/>
-      <x:c r="K52" s="15"/>
+      <x:c r="H52" s="14"/>
+      <x:c r="I52" s="14"/>
+      <x:c r="J52" s="14"/>
+      <x:c r="K52" s="14"/>
       <x:c r="L52" s="13"/>
       <x:c r="M52" s="15"/>
       <x:c r="N52" s="13"/>
@@ -2024,6 +2240,10 @@
       <x:c r="AA52" s="15"/>
       <x:c r="AB52" s="13"/>
       <x:c r="AC52" s="15"/>
+      <x:c r="AD52" s="13"/>
+      <x:c r="AE52" s="15"/>
+      <x:c r="AF52" s="13"/>
+      <x:c r="AG52" s="15"/>
     </x:row>
     <x:row r="53" ht="25" customHeight="1">
       <x:c r="A53" s="12"/>
@@ -2033,10 +2253,10 @@
       <x:c r="E53" s="14"/>
       <x:c r="F53" s="14"/>
       <x:c r="G53" s="14"/>
-      <x:c r="H53" s="13"/>
-      <x:c r="I53" s="15"/>
-      <x:c r="J53" s="13"/>
-      <x:c r="K53" s="15"/>
+      <x:c r="H53" s="14"/>
+      <x:c r="I53" s="14"/>
+      <x:c r="J53" s="14"/>
+      <x:c r="K53" s="14"/>
       <x:c r="L53" s="13"/>
       <x:c r="M53" s="15"/>
       <x:c r="N53" s="13"/>
@@ -2055,6 +2275,10 @@
       <x:c r="AA53" s="15"/>
       <x:c r="AB53" s="13"/>
       <x:c r="AC53" s="15"/>
+      <x:c r="AD53" s="13"/>
+      <x:c r="AE53" s="15"/>
+      <x:c r="AF53" s="13"/>
+      <x:c r="AG53" s="15"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2063,7 +2287,11 @@
     <x:mergeCell ref="C1:D1"/>
     <x:mergeCell ref="E1:F1"/>
     <x:mergeCell ref="G1:G2"/>
-    <x:mergeCell ref="H1:AC1"/>
+    <x:mergeCell ref="H1:H2"/>
+    <x:mergeCell ref="I1:I2"/>
+    <x:mergeCell ref="J1:J2"/>
+    <x:mergeCell ref="K1:K2"/>
+    <x:mergeCell ref="L1:AG1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
